--- a/data/feishu/lingxing_mcp_tools.xlsx
+++ b/data/feishu/lingxing_mcp_tools.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -2215,7 +2215,10 @@
 uid</t>
   </si>
   <si>
-    <t xml:space="preserve">store_sid
+    <t xml:space="preserve">sids=508344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">store_id（即sid）
 msku
 asin
 fnsku</t>
@@ -2232,8 +2235,7 @@
 store_id</t>
   </si>
   <si>
-    <t xml:space="preserve">s_id
-store_id
+    <t xml:space="preserve">store_id（即sid）
 </t>
   </si>
 </sst>
@@ -2480,7 +2482,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="73">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2625,9 +2627,6 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="10" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2643,9 +2642,6 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="12" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="true"/>
     </xf>
@@ -2661,9 +2657,6 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="12" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="12" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="13" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="true"/>
     </xf>
@@ -2679,9 +2672,6 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="13" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="13" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="14" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="true"/>
     </xf>
@@ -2694,9 +2684,6 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="14" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="14" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="15" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="true"/>
     </xf>
@@ -2704,12 +2691,12 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="15" fontId="2" numFmtId="0" xfId="0">
+      <alignment vertical="top" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="15" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="14" fontId="3" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="15" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="15" fontId="2" numFmtId="0" xfId="0">
@@ -3035,13 +3022,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="18"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="8" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="8" min="8" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5063,13 +5050,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="18"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="39"/>
     <col collapsed="false" customWidth="true" hidden="false" max="7" min="7" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" max="8" min="8" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="31"/>
     <col collapsed="false" customWidth="true" hidden="false" max="10" min="10" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5137,17 +5124,17 @@
         <v>245</v>
       </c>
       <c r="K2" s="47"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
     </row>
     <row customHeight="true" ht="40" r="3">
       <c r="A3" s="44"/>
@@ -5171,17 +5158,17 @@
         <v>250</v>
       </c>
       <c r="K3" s="47"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
     </row>
     <row customHeight="true" ht="40" r="4">
       <c r="A4" s="44"/>
@@ -5201,373 +5188,373 @@
       <c r="I4" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="J4" s="49" t="s">
+      <c r="J4" s="48" t="s">
         <v>253</v>
       </c>
       <c r="K4" s="47"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
     </row>
     <row customHeight="true" ht="40" r="5">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>255</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="49" t="s">
         <v>257</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="49" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="50" t="s">
         <v>261</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="J5" s="52" t="s">
+      <c r="J5" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="K5" s="53"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
     </row>
     <row customHeight="true" ht="40" r="6">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="49" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="49" t="s">
         <v>265</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="49" t="s">
         <v>267</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="K6" s="53"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="52"/>
+      <c r="V6" s="52"/>
     </row>
     <row customHeight="true" ht="40" r="7">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="49" t="s">
         <v>273</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="G7" s="50" t="s">
+      <c r="G7" s="49" t="s">
         <v>260</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="50" t="s">
         <v>274</v>
       </c>
-      <c r="I7" s="52" t="s">
+      <c r="I7" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="J7" s="52" t="s">
+      <c r="J7" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="K7" s="53"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="54"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="52"/>
     </row>
     <row customHeight="true" ht="40" r="8">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>254</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="53" t="s">
         <v>276</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="53" t="s">
         <v>277</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="F8" s="55" t="s">
+      <c r="F8" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="G8" s="56" t="s">
+      <c r="G8" s="54" t="s">
         <v>279</v>
       </c>
-      <c r="H8" s="55" t="s">
+      <c r="H8" s="53" t="s">
         <v>248</v>
       </c>
-      <c r="I8" s="57" t="s">
+      <c r="I8" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="J8" s="58" t="s">
+      <c r="J8" s="56" t="s">
         <v>250</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="60"/>
-      <c r="U8" s="60"/>
-      <c r="V8" s="60"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="57"/>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="57"/>
     </row>
     <row customHeight="true" ht="40" r="9">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="59" t="s">
         <v>282</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="D9" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="E9" s="59" t="s">
         <v>285</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="58" t="s">
         <v>286</v>
       </c>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="58" t="s">
         <v>287</v>
       </c>
-      <c r="H9" s="61" t="s">
+      <c r="H9" s="58" t="s">
         <v>288</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="60" t="s">
         <v>289</v>
       </c>
-      <c r="J9" s="64" t="s">
+      <c r="J9" s="61" t="s">
         <v>290</v>
       </c>
-      <c r="K9" s="65"/>
-      <c r="L9" s="66"/>
-      <c r="M9" s="66"/>
-      <c r="N9" s="66"/>
-      <c r="O9" s="66"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="66"/>
-      <c r="S9" s="66"/>
-      <c r="T9" s="66"/>
-      <c r="U9" s="66"/>
-      <c r="V9" s="66"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
     </row>
     <row customHeight="true" ht="40" r="10">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="63" t="s">
         <v>291</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="63" t="s">
         <v>292</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="63" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="F10" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="H10" s="67" t="s">
+      <c r="H10" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="I10" s="68" t="s">
+      <c r="I10" s="64" t="s">
         <v>295</v>
       </c>
-      <c r="J10" s="69" t="s">
+      <c r="J10" s="65" t="s">
         <v>250</v>
       </c>
-      <c r="K10" s="70"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="71"/>
-      <c r="U10" s="71"/>
-      <c r="V10" s="71"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
     </row>
     <row customHeight="true" ht="40" r="11">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="67" t="s">
         <v>291</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="68" t="s">
         <v>296</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="68" t="s">
         <v>297</v>
       </c>
-      <c r="D11" s="73" t="s">
+      <c r="D11" s="68" t="s">
         <v>298</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="68" t="s">
         <v>299</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="69" t="s">
+        <v>300</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="H11" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="I11" s="70" t="s">
+        <v>295</v>
+      </c>
+      <c r="J11" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="72"/>
+      <c r="U11" s="72"/>
+      <c r="V11" s="72"/>
+    </row>
+    <row customHeight="true" ht="40" r="12">
+      <c r="A12" s="67" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="68" t="s">
         <v>278</v>
       </c>
-      <c r="G11" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="H11" s="67" t="s">
+      <c r="E12" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="H12" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="I11" s="74" t="s">
+      <c r="I12" s="70" t="s">
         <v>295</v>
       </c>
-      <c r="J11" s="75" t="s">
+      <c r="J12" s="71" t="s">
         <v>250</v>
       </c>
-      <c r="K11" s="76"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="77"/>
-      <c r="S11" s="77"/>
-      <c r="T11" s="77"/>
-      <c r="U11" s="77"/>
-      <c r="V11" s="77"/>
-    </row>
-    <row customHeight="true" ht="40" r="12">
-      <c r="A12" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="73" t="s">
-        <v>301</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="D12" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>303</v>
-      </c>
-      <c r="F12" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="G12" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="H12" s="67" t="s">
-        <v>248</v>
-      </c>
-      <c r="I12" s="74" t="s">
-        <v>295</v>
-      </c>
-      <c r="J12" s="75" t="s">
-        <v>250</v>
-      </c>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="77"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="77"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
     </row>
     <row r="13">
       <c r="A13" s="43"/>
